--- a/annotation/a591.xlsx
+++ b/annotation/a591.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mots" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horizontales" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verticales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeletedCells" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,36 +450,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>kalima_text</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>num_sora</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sora_name_ar</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>aya_no</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>kalima_text_emlaey</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -494,34 +465,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>وَٱلسَّمَآءِ</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>86</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>والسماء</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -538,34 +485,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>وَٱلطَّارِقِ</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>86</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>والطارق</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -582,34 +505,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>وَمَآ</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>86</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>وما</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -626,34 +525,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>أَدۡرَىٰكَ</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>86</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>أدراك</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -670,34 +545,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>مَا</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>86</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ما</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -714,34 +565,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ٱلطَّارِقُ</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>86</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>الطارق</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -758,34 +585,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ٱلنَّجۡمُ</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>86</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>النجم</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -802,34 +605,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ٱلثَّاقِبُ</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>86</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>الثاقب</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -846,34 +625,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>إِن</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>86</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>إن</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -890,34 +645,10 @@
         <v>163.7768595041322</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>كُلُّ</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>86</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>كل</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -934,34 +665,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>نَفۡسٖ</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>86</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>نفس</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -978,34 +685,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>لَّمَّا</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>86</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>لما</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1022,34 +705,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>عَلَيۡهَا</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>86</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>عليها</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1066,34 +725,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>حَافِظٞ</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>86</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>حافظ</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -1110,34 +745,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>فَلۡيَنظُرِ</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>86</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>فلينظر</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1154,34 +765,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ٱلۡإِنسَٰنُ</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>86</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>الإنسان</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1198,34 +785,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>مِمَّ</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>86</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>مم</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1242,34 +805,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>خُلِقَ</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>86</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>خلق</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -1286,34 +825,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>خُلِقَ</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>86</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>خلق</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1330,34 +845,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>مِن</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>86</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>6</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>من</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1374,34 +865,10 @@
         <v>216.5371900826446</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>مَّآءٖ</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>86</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ماء</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1418,34 +885,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>دَافِقٖ</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>86</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>دافق</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1462,34 +905,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>يَخۡرُجُ</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>86</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>يخرج</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -1506,34 +925,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>مِنۢ</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>86</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>من</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1550,34 +945,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>بَيۡنِ</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>86</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>بين</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1594,34 +965,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ٱلصُّلۡبِ</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>86</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>الصلب</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1638,34 +985,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>وَٱلتَّرَآئِبِ</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>86</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>والترائب</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -1682,34 +1005,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>إِنَّهُۥ</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>86</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>إنه</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1726,34 +1025,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>عَلَىٰ</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>86</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>8</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>على</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -1770,34 +1045,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>رَجۡعِهِۦ</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>86</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>رجعه</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -1814,34 +1065,10 @@
         <v>267.099173553719</v>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>38</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>لَقَادِرٞ</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>86</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>8</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>لقادر</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -1858,34 +1085,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>39</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>يَوۡمَ</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>86</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>يوم</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -1902,34 +1105,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>تُبۡلَى</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>86</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>تبلى</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
@@ -1946,34 +1125,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>41</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ٱلسَّرَآئِرُ</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>86</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>السرائر</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -1990,34 +1145,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>فَمَا</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>86</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>فما</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -2034,34 +1165,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>لَهُۥ</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>86</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>10</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>له</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -2078,34 +1185,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>45</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>مِن</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>86</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>من</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -2122,34 +1205,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>قُوَّةٖ</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>86</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>10</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>قوة</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -2166,34 +1225,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>47</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>وَلَا</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>86</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>10</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>ولا</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -2210,34 +1245,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>49</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>نَاصِرٖ</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>86</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>10</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>ناصر</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -2254,34 +1265,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>وَٱلسَّمَآءِ</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>86</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>11</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>والسماء</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -2298,34 +1285,10 @@
         <v>319.8595041322314</v>
       </c>
       <c r="E43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>51</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ذَاتِ</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>86</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>11</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>ذات</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -2342,34 +1305,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>52</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ٱلرَّجۡعِ</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>86</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>11</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>الرجع</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -2386,34 +1325,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>53</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>وَٱلۡأَرۡضِ</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>86</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>12</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>والأرض</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -2430,34 +1345,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>54</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>ذَاتِ</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>86</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>12</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>ذات</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -2474,34 +1365,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>56</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>ٱلصَّدۡعِ</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>86</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>12</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>الصدع</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
@@ -2518,34 +1385,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>57</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>إِنَّهُۥ</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>86</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>13</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>إنه</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49">
@@ -2562,34 +1405,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>58</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>لَقَوۡلٞ</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>86</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>13</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>لقول</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -2606,34 +1425,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>60</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>فَصۡلٞ</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>86</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>13</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>فصل</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
@@ -2650,34 +1445,10 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>61</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>وَمَا</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>86</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>14</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>وما</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52">
@@ -2694,2806 +1465,1250 @@
         <v>371.5206611570247</v>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>62</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>هُوَ</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>86</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>14</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>هو</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
+        <v>7.694214876033057</v>
+      </c>
+      <c r="B53" t="n">
+        <v>319.8595041322314</v>
+      </c>
+      <c r="C53" t="n">
         <v>43.96694214876032</v>
-      </c>
-      <c r="B53" t="n">
-        <v>319.8595041322314</v>
-      </c>
-      <c r="C53" t="n">
-        <v>76.94214876033057</v>
       </c>
       <c r="D53" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="E53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>63</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>بِٱلۡهَزۡلِ</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>86</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>14</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>بالهزل</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>7.694214876033057</v>
+        <v>437.4710743801652</v>
       </c>
       <c r="B54" t="n">
-        <v>319.8595041322314</v>
+        <v>371.5206611570247</v>
       </c>
       <c r="C54" t="n">
-        <v>43.96694214876032</v>
+        <v>503.4214876033058</v>
       </c>
       <c r="D54" t="n">
-        <v>371.5206611570247</v>
+        <v>426.4793388429752</v>
       </c>
       <c r="E54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>64</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>إِنَّهُمۡ</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>86</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>15</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>إنهم</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>437.4710743801652</v>
+        <v>403.396694214876</v>
       </c>
       <c r="B55" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C55" t="n">
-        <v>503.4214876033058</v>
+        <v>437.4710743801652</v>
       </c>
       <c r="D55" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>65</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>يَكِيدُونَ</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>86</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>15</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>يكيدون</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>403.396694214876</v>
+        <v>326.4545454545454</v>
       </c>
       <c r="B56" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C56" t="n">
-        <v>437.4710743801652</v>
+        <v>369.3223140495867</v>
       </c>
       <c r="D56" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>66</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>كَيۡدٗا</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>86</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>كيدا</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>326.4545454545454</v>
+        <v>290.1818181818181</v>
       </c>
       <c r="B57" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C57" t="n">
-        <v>369.3223140495867</v>
+        <v>326.4545454545454</v>
       </c>
       <c r="D57" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>68</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>وَأَكِيدُ</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>86</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>16</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>وأكيد</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>290.1818181818181</v>
+        <v>216.5371900826446</v>
       </c>
       <c r="B58" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C58" t="n">
-        <v>326.4545454545454</v>
+        <v>257.2066115702479</v>
       </c>
       <c r="D58" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>69</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>كَيۡدٗا</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>86</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>16</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>كيدا</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>216.5371900826446</v>
+        <v>147.2892561983471</v>
       </c>
       <c r="B59" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C59" t="n">
-        <v>257.2066115702479</v>
+        <v>216.5371900826446</v>
       </c>
       <c r="D59" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>71</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>فَمَهِّلِ</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>86</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>17</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>فمهل</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>147.2892561983471</v>
+        <v>92.33057851239668</v>
       </c>
       <c r="B60" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C60" t="n">
-        <v>216.5371900826446</v>
+        <v>147.2892561983471</v>
       </c>
       <c r="D60" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>72</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>ٱلۡكَٰفِرِينَ</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>86</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>17</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>الكافرين</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>92.33057851239668</v>
+        <v>46.16528925619834</v>
       </c>
       <c r="B61" t="n">
         <v>371.5206611570247</v>
       </c>
       <c r="C61" t="n">
-        <v>147.2892561983471</v>
+        <v>92.33057851239668</v>
       </c>
       <c r="D61" t="n">
         <v>426.4793388429752</v>
       </c>
       <c r="E61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>73</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>أَمۡهِلۡهُمۡ</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>86</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>17</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>أمهلهم</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>46.16528925619834</v>
+        <v>436.3719008264462</v>
       </c>
       <c r="B62" t="n">
-        <v>371.5206611570247</v>
+        <v>535.297520661157</v>
       </c>
       <c r="C62" t="n">
-        <v>92.33057851239668</v>
+        <v>471.5454545454545</v>
       </c>
       <c r="D62" t="n">
-        <v>426.4793388429752</v>
+        <v>583.6611570247933</v>
       </c>
       <c r="E62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>74</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>رُوَيۡدَۢا</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>86</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>الطَّارق</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>17</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>رويدا</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>436.3719008264462</v>
+        <v>401.198347107438</v>
       </c>
       <c r="B63" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C63" t="n">
-        <v>471.5454545454545</v>
+        <v>436.3719008264462</v>
       </c>
       <c r="D63" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>75</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>سَبِّحِ</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>87</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>النَّبَإ</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>سبح</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>401.198347107438</v>
+        <v>370.4214876033058</v>
       </c>
       <c r="B64" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C64" t="n">
-        <v>436.3719008264462</v>
+        <v>401.198347107438</v>
       </c>
       <c r="D64" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>76</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>ٱسۡمَ</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>87</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>اسم</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>370.4214876033058</v>
+        <v>326.4545454545454</v>
       </c>
       <c r="B65" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C65" t="n">
-        <v>401.198347107438</v>
+        <v>370.4214876033058</v>
       </c>
       <c r="D65" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>77</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>رَبِّكَ</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>87</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>ربك</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>326.4545454545454</v>
+        <v>259.4049586776859</v>
       </c>
       <c r="B66" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C66" t="n">
-        <v>370.4214876033058</v>
+        <v>294.5785123966942</v>
       </c>
       <c r="D66" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>78</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>ٱلۡأَعۡلَى</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>87</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>259.4049586776859</v>
+        <v>227.5289256198347</v>
       </c>
       <c r="B67" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C67" t="n">
-        <v>294.5785123966942</v>
+        <v>259.4049586776859</v>
       </c>
       <c r="D67" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>80</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>ٱلَّذِي</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>87</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>الذي</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>227.5289256198347</v>
+        <v>189.0578512396694</v>
       </c>
       <c r="B68" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C68" t="n">
-        <v>259.4049586776859</v>
+        <v>227.5289256198347</v>
       </c>
       <c r="D68" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>81</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>خَلَقَ</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>87</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>2</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>خلق</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>189.0578512396694</v>
+        <v>116.5123966942149</v>
       </c>
       <c r="B69" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C69" t="n">
-        <v>227.5289256198347</v>
+        <v>157.1818181818182</v>
       </c>
       <c r="D69" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>82</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>فَسَوَّىٰ</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>87</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>2</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>فسوى</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>116.5123966942149</v>
+        <v>90.13223140495867</v>
       </c>
       <c r="B70" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C70" t="n">
-        <v>157.1818181818182</v>
+        <v>116.5123966942149</v>
       </c>
       <c r="D70" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>84</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>وَٱلَّذِي</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>87</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>والذي</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>90.13223140495867</v>
+        <v>46.16528925619834</v>
       </c>
       <c r="B71" t="n">
         <v>535.297520661157</v>
       </c>
       <c r="C71" t="n">
-        <v>116.5123966942149</v>
+        <v>90.13223140495867</v>
       </c>
       <c r="D71" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="E71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>85</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>قَدَّرَ</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>87</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>3</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>قدر</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>46.16528925619834</v>
+        <v>448.4628099173553</v>
       </c>
       <c r="B72" t="n">
-        <v>535.297520661157</v>
+        <v>583.6611570247933</v>
       </c>
       <c r="C72" t="n">
-        <v>90.13223140495867</v>
+        <v>501.2231404958677</v>
       </c>
       <c r="D72" t="n">
-        <v>583.6611570247933</v>
+        <v>634.2231404958677</v>
       </c>
       <c r="E72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>86</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>فَهَدَىٰ</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>87</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>3</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>فهدى</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>448.4628099173553</v>
+        <v>409.99173553719</v>
       </c>
       <c r="B73" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C73" t="n">
-        <v>501.2231404958677</v>
+        <v>448.4628099173553</v>
       </c>
       <c r="D73" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>87</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>وَٱلَّذِيٓ</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>87</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>4</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>والذي</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>409.99173553719</v>
+        <v>368.2231404958677</v>
       </c>
       <c r="B74" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C74" t="n">
-        <v>448.4628099173553</v>
+        <v>409.99173553719</v>
       </c>
       <c r="D74" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>88</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>أَخۡرَجَ</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>87</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>أخرج</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>368.2231404958677</v>
+        <v>284.6859504132231</v>
       </c>
       <c r="B75" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C75" t="n">
-        <v>409.99173553719</v>
+        <v>334.1487603305785</v>
       </c>
       <c r="D75" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>89</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>ٱلۡمَرۡعَىٰ</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>87</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>4</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>المرعى</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>284.6859504132231</v>
+        <v>250.6115702479339</v>
       </c>
       <c r="B76" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C76" t="n">
-        <v>334.1487603305785</v>
+        <v>284.6859504132231</v>
       </c>
       <c r="D76" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>91</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>فَجَعَلَهُۥ</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>87</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>5</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>فجعله</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>250.6115702479339</v>
+        <v>207.7438016528925</v>
       </c>
       <c r="B77" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C77" t="n">
-        <v>284.6859504132231</v>
+        <v>250.6115702479339</v>
       </c>
       <c r="D77" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>92</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>غُثَآءً</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>87</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>5</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>غثاء</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>207.7438016528925</v>
+        <v>106.6198347107438</v>
       </c>
       <c r="B78" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C78" t="n">
-        <v>250.6115702479339</v>
+        <v>173.6694214876033</v>
       </c>
       <c r="D78" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>93</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>أَحۡوَىٰ</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>87</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>5</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>أحوى</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>106.6198347107438</v>
+        <v>82.43801652892562</v>
       </c>
       <c r="B79" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C79" t="n">
-        <v>173.6694214876033</v>
+        <v>106.6198347107438</v>
       </c>
       <c r="D79" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>95</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>سَنُقۡرِئُكَ</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
         <v>87</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>6</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>سنقرئك</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>82.43801652892562</v>
+        <v>46.16528925619834</v>
       </c>
       <c r="B80" t="n">
         <v>583.6611570247933</v>
       </c>
       <c r="C80" t="n">
-        <v>106.6198347107438</v>
+        <v>82.43801652892562</v>
       </c>
       <c r="D80" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="E80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>96</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>فَلَا</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>87</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>6</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>فلا</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>46.16528925619834</v>
+        <v>471.5454545454545</v>
       </c>
       <c r="B81" t="n">
-        <v>583.6611570247933</v>
+        <v>634.2231404958677</v>
       </c>
       <c r="C81" t="n">
-        <v>82.43801652892562</v>
+        <v>502.3223140495867</v>
       </c>
       <c r="D81" t="n">
-        <v>634.2231404958677</v>
+        <v>686.9834710743801</v>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>97</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>تَنسَىٰٓ</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>87</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>6</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>تنسى</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
+        <v>455.0578512396694</v>
+      </c>
+      <c r="B82" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C82" t="n">
         <v>471.5454545454545</v>
       </c>
-      <c r="B82" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C82" t="n">
-        <v>502.3223140495867</v>
-      </c>
       <c r="D82" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>98</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>إِلَّا</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>87</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>7</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>إلا</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
+        <v>426.4793388429752</v>
+      </c>
+      <c r="B83" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C83" t="n">
         <v>455.0578512396694</v>
       </c>
-      <c r="B83" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C83" t="n">
-        <v>471.5454545454545</v>
-      </c>
       <c r="D83" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>99</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>مَا</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>87</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>7</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>ما</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
+        <v>396.8016528925619</v>
+      </c>
+      <c r="B84" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C84" t="n">
         <v>426.4793388429752</v>
       </c>
-      <c r="B84" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C84" t="n">
-        <v>455.0578512396694</v>
-      </c>
       <c r="D84" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>100</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>شَآءَ</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>87</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>7</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>شاء</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
+        <v>369.3223140495867</v>
+      </c>
+      <c r="B85" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C85" t="n">
         <v>396.8016528925619</v>
       </c>
-      <c r="B85" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C85" t="n">
-        <v>426.4793388429752</v>
-      </c>
       <c r="D85" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>101</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>ٱللَّهُۚ</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>87</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>الله</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
+        <v>339.6446280991735</v>
+      </c>
+      <c r="B86" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C86" t="n">
         <v>369.3223140495867</v>
       </c>
-      <c r="B86" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C86" t="n">
-        <v>396.8016528925619</v>
-      </c>
       <c r="D86" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>102</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>إِنَّهُۥ</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>87</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>7</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>إنه</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
+        <v>298.9752066115702</v>
+      </c>
+      <c r="B87" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C87" t="n">
         <v>339.6446280991735</v>
       </c>
-      <c r="B87" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C87" t="n">
-        <v>369.3223140495867</v>
-      </c>
       <c r="D87" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>103</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>يَعۡلَمُ</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>87</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>7</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>يعلم</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>275.8925619834711</v>
+      </c>
+      <c r="B88" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C88" t="n">
         <v>298.9752066115702</v>
       </c>
-      <c r="B88" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C88" t="n">
-        <v>339.6446280991735</v>
-      </c>
       <c r="D88" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>104</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>ٱلۡجَهۡرَ</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>87</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>7</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>الجهر</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>237.4214876033058</v>
+      </c>
+      <c r="B89" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C89" t="n">
         <v>275.8925619834711</v>
       </c>
-      <c r="B89" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C89" t="n">
-        <v>298.9752066115702</v>
-      </c>
       <c r="D89" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>105</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>وَمَا</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>87</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>7</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>وما</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>237.4214876033058</v>
+        <v>141.793388429752</v>
       </c>
       <c r="B90" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="C90" t="n">
-        <v>275.8925619834711</v>
+        <v>204.4462809917355</v>
       </c>
       <c r="D90" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>106</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>يَخۡفَىٰ</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>87</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>7</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>يخفى</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
+        <v>86.83471074380165</v>
+      </c>
+      <c r="B91" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C91" t="n">
         <v>141.793388429752</v>
       </c>
-      <c r="B91" t="n">
-        <v>634.2231404958677</v>
-      </c>
-      <c r="C91" t="n">
-        <v>204.4462809917355</v>
-      </c>
       <c r="D91" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>108</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>وَنُيَسِّرُكَ</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>87</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>8</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>ونيسرك</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>86.83471074380165</v>
+        <v>10.99173553719008</v>
       </c>
       <c r="B92" t="n">
         <v>634.2231404958677</v>
       </c>
       <c r="C92" t="n">
-        <v>141.793388429752</v>
+        <v>52.7603305785124</v>
       </c>
       <c r="D92" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="E92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>109</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>لِلۡيُسۡرَىٰ</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>87</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>8</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>لليسرى</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>10.99173553719008</v>
+        <v>479.2396694214876</v>
       </c>
       <c r="B93" t="n">
-        <v>634.2231404958677</v>
+        <v>686.9834710743801</v>
       </c>
       <c r="C93" t="n">
-        <v>52.7603305785124</v>
+        <v>503.4214876033058</v>
       </c>
       <c r="D93" t="n">
-        <v>686.9834710743801</v>
+        <v>741.9421487603305</v>
       </c>
       <c r="E93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>111</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>فَذَكِّرۡ</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>87</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>9</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>فذكر</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
+        <v>430.8760330578512</v>
+      </c>
+      <c r="B94" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C94" t="n">
         <v>479.2396694214876</v>
       </c>
-      <c r="B94" t="n">
-        <v>686.9834710743801</v>
-      </c>
-      <c r="C94" t="n">
-        <v>503.4214876033058</v>
-      </c>
       <c r="D94" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>112</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>إِن</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>87</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>9</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>إن</t>
-        </is>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
+        <v>375.9173553719008</v>
+      </c>
+      <c r="B95" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C95" t="n">
         <v>430.8760330578512</v>
       </c>
-      <c r="B95" t="n">
-        <v>686.9834710743801</v>
-      </c>
-      <c r="C95" t="n">
-        <v>479.2396694214876</v>
-      </c>
       <c r="D95" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>113</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>نَّفَعَتِ</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
-        <v>87</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>9</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>نفعت</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>375.9173553719008</v>
+        <v>293.4793388429752</v>
       </c>
       <c r="B96" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="C96" t="n">
-        <v>430.8760330578512</v>
+        <v>345.1404958677685</v>
       </c>
       <c r="D96" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>114</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>ٱلذِّكۡرَىٰ</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
-        <v>87</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>9</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>الذكرى</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
+        <v>272.595041322314</v>
+      </c>
+      <c r="B97" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C97" t="n">
         <v>293.4793388429752</v>
       </c>
-      <c r="B97" t="n">
-        <v>686.9834710743801</v>
-      </c>
-      <c r="C97" t="n">
-        <v>345.1404958677685</v>
-      </c>
       <c r="D97" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>116</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>سَيَذَّكَّرُ</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>87</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>10</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>سيذكر</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
+        <v>231.9256198347107</v>
+      </c>
+      <c r="B98" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C98" t="n">
         <v>272.595041322314</v>
       </c>
-      <c r="B98" t="n">
-        <v>686.9834710743801</v>
-      </c>
-      <c r="C98" t="n">
-        <v>293.4793388429752</v>
-      </c>
       <c r="D98" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>117</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>مَن</t>
-        </is>
-      </c>
-      <c r="H98" t="n">
-        <v>87</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>10</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>من</t>
-        </is>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>231.9256198347107</v>
+        <v>137.396694214876</v>
       </c>
       <c r="B99" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="C99" t="n">
-        <v>272.595041322314</v>
+        <v>200.0495867768595</v>
       </c>
       <c r="D99" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>118</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>يَخۡشَىٰ</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
-        <v>87</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>10</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>يخشى</t>
-        </is>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
+        <v>83.53719008264461</v>
+      </c>
+      <c r="B100" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C100" t="n">
         <v>137.396694214876</v>
       </c>
-      <c r="B100" t="n">
-        <v>686.9834710743801</v>
-      </c>
-      <c r="C100" t="n">
-        <v>200.0495867768595</v>
-      </c>
       <c r="D100" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>120</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>وَيَتَجَنَّبُهَا</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>87</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>11</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>ويتجنبها</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>83.53719008264461</v>
+        <v>9.892561983471074</v>
       </c>
       <c r="B101" t="n">
         <v>686.9834710743801</v>
       </c>
       <c r="C101" t="n">
-        <v>137.396694214876</v>
+        <v>51.66115702479338</v>
       </c>
       <c r="D101" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="E101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>121</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>ٱلۡأَشۡقَى</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
-        <v>87</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>11</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>الأشقى</t>
-        </is>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>9.892561983471074</v>
+        <v>461.6528925619834</v>
       </c>
       <c r="B102" t="n">
-        <v>686.9834710743801</v>
+        <v>741.9421487603305</v>
       </c>
       <c r="C102" t="n">
-        <v>51.66115702479338</v>
+        <v>505.6198347107438</v>
       </c>
       <c r="D102" t="n">
-        <v>741.9421487603305</v>
+        <v>795.8016528925619</v>
       </c>
       <c r="E102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>123</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>ٱلَّذِي</t>
-        </is>
-      </c>
-      <c r="H102" t="n">
-        <v>87</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>12</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>الذي</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
+        <v>430.8760330578512</v>
+      </c>
+      <c r="B103" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C103" t="n">
         <v>461.6528925619834</v>
-      </c>
-      <c r="B103" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C103" t="n">
-        <v>505.6198347107438</v>
       </c>
       <c r="D103" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>124</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>يَصۡلَى</t>
-        </is>
-      </c>
-      <c r="H103" t="n">
-        <v>87</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>12</v>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>يصلى</t>
-        </is>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
+        <v>378.1157024793388</v>
+      </c>
+      <c r="B104" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C104" t="n">
         <v>430.8760330578512</v>
-      </c>
-      <c r="B104" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C104" t="n">
-        <v>461.6528925619834</v>
       </c>
       <c r="D104" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>125</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>ٱلنَّارَ</t>
-        </is>
-      </c>
-      <c r="H104" t="n">
-        <v>87</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>12</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>النار</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>378.1157024793388</v>
+        <v>326.4545454545454</v>
       </c>
       <c r="B105" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="C105" t="n">
-        <v>430.8760330578512</v>
+        <v>345.1404958677685</v>
       </c>
       <c r="D105" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>126</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>ٱلۡكُبۡرَىٰ</t>
-        </is>
-      </c>
-      <c r="H105" t="n">
-        <v>87</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>12</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>الكبرى</t>
-        </is>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
+        <v>309.9669421487603</v>
+      </c>
+      <c r="B106" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C106" t="n">
         <v>326.4545454545454</v>
-      </c>
-      <c r="B106" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C106" t="n">
-        <v>345.1404958677685</v>
       </c>
       <c r="D106" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>128</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>ثُمَّ</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
-        <v>87</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>13</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>ثم</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
+        <v>267.099173553719</v>
+      </c>
+      <c r="B107" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C107" t="n">
         <v>309.9669421487603</v>
-      </c>
-      <c r="B107" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C107" t="n">
-        <v>326.4545454545454</v>
       </c>
       <c r="D107" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>129</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>لَا</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
-        <v>87</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>13</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>267.099173553719</v>
+        <v>242.9173553719008</v>
       </c>
       <c r="B108" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="C108" t="n">
-        <v>309.9669421487603</v>
+        <v>267.099173553719</v>
       </c>
       <c r="D108" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>130</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>يَمُوتُ</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>87</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>13</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>يموت</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
+        <v>218.7355371900826</v>
+      </c>
+      <c r="B109" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C109" t="n">
         <v>242.9173553719008</v>
-      </c>
-      <c r="B109" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C109" t="n">
-        <v>267.099173553719</v>
       </c>
       <c r="D109" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>131</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>فِيهَا</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>87</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>13</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>فيها</t>
-        </is>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
+        <v>186.8595041322314</v>
+      </c>
+      <c r="B110" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C110" t="n">
         <v>218.7355371900826</v>
-      </c>
-      <c r="B110" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C110" t="n">
-        <v>242.9173553719008</v>
       </c>
       <c r="D110" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>132</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>وَلَا</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
-        <v>87</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>13</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>ولا</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>186.8595041322314</v>
+        <v>135.198347107438</v>
       </c>
       <c r="B111" t="n">
         <v>741.9421487603305</v>
       </c>
       <c r="C111" t="n">
-        <v>218.7355371900826</v>
+        <v>153.8842975206611</v>
       </c>
       <c r="D111" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>133</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>يَحۡيَىٰ</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
-        <v>87</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>13</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>يحيا</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
+        <v>102.2231404958678</v>
+      </c>
+      <c r="B112" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C112" t="n">
         <v>135.198347107438</v>
-      </c>
-      <c r="B112" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C112" t="n">
-        <v>153.8842975206611</v>
       </c>
       <c r="D112" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>135</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>قَدۡ</t>
-        </is>
-      </c>
-      <c r="H112" t="n">
-        <v>87</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>14</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>قد</t>
-        </is>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
+        <v>78.04132231404958</v>
+      </c>
+      <c r="B113" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C113" t="n">
         <v>102.2231404958678</v>
-      </c>
-      <c r="B113" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C113" t="n">
-        <v>135.198347107438</v>
       </c>
       <c r="D113" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>136</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>أَفۡلَحَ</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
-        <v>87</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>14</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>أفلح</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
+        <v>46.16528925619834</v>
+      </c>
+      <c r="B114" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C114" t="n">
         <v>78.04132231404958</v>
-      </c>
-      <c r="B114" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C114" t="n">
-        <v>102.2231404958678</v>
       </c>
       <c r="D114" t="n">
         <v>795.8016528925619</v>
       </c>
       <c r="E114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>137</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>مَن</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
-        <v>87</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>14</v>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>من</t>
-        </is>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>46.16528925619834</v>
-      </c>
-      <c r="B115" t="n">
-        <v>741.9421487603305</v>
-      </c>
-      <c r="C115" t="n">
-        <v>78.04132231404958</v>
-      </c>
-      <c r="D115" t="n">
-        <v>795.8016528925619</v>
-      </c>
-      <c r="E115" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>138</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>تَزَكَّىٰ</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>87</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>الأعلى</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>14</v>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>تزكى</t>
-        </is>
-      </c>
-      <c r="L115" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -7255,4 +4470,362 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>y1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>181.3636363636363</v>
+      </c>
+      <c r="B2" t="n">
+        <v>216.5371900826446</v>
+      </c>
+      <c r="C2" t="n">
+        <v>214.3388429752066</v>
+      </c>
+      <c r="D2" t="n">
+        <v>267.099173553719</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>357.2314049586777</v>
+      </c>
+      <c r="B3" t="n">
+        <v>111.0165289256198</v>
+      </c>
+      <c r="C3" t="n">
+        <v>389.1074380165289</v>
+      </c>
+      <c r="D3" t="n">
+        <v>163.7768595041322</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>182.4628099173553</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111.0165289256198</v>
+      </c>
+      <c r="C4" t="n">
+        <v>217.6363636363636</v>
+      </c>
+      <c r="D4" t="n">
+        <v>163.7768595041322</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>52.7603305785124</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111.0165289256198</v>
+      </c>
+      <c r="C5" t="n">
+        <v>86.83471074380165</v>
+      </c>
+      <c r="D5" t="n">
+        <v>163.7768595041322</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>317.6611570247933</v>
+      </c>
+      <c r="B6" t="n">
+        <v>163.7768595041322</v>
+      </c>
+      <c r="C6" t="n">
+        <v>351.7355371900826</v>
+      </c>
+      <c r="D6" t="n">
+        <v>216.5371900826446</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106.6198347107438</v>
+      </c>
+      <c r="B7" t="n">
+        <v>163.7768595041322</v>
+      </c>
+      <c r="C7" t="n">
+        <v>141.793388429752</v>
+      </c>
+      <c r="D7" t="n">
+        <v>216.5371900826446</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>428.6776859504132</v>
+      </c>
+      <c r="B8" t="n">
+        <v>216.5371900826446</v>
+      </c>
+      <c r="C8" t="n">
+        <v>460.5537190082644</v>
+      </c>
+      <c r="D8" t="n">
+        <v>267.099173553719</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>311.0661157024793</v>
+      </c>
+      <c r="B9" t="n">
+        <v>319.8595041322314</v>
+      </c>
+      <c r="C9" t="n">
+        <v>342.9421487603306</v>
+      </c>
+      <c r="D9" t="n">
+        <v>371.5206611570247</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>170.3719008264463</v>
+      </c>
+      <c r="B10" t="n">
+        <v>319.8595041322314</v>
+      </c>
+      <c r="C10" t="n">
+        <v>201.1487603305785</v>
+      </c>
+      <c r="D10" t="n">
+        <v>371.5206611570247</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>43.96694214876032</v>
+      </c>
+      <c r="B11" t="n">
+        <v>319.8595041322314</v>
+      </c>
+      <c r="C11" t="n">
+        <v>76.94214876033057</v>
+      </c>
+      <c r="D11" t="n">
+        <v>371.5206611570247</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>369.3223140495867</v>
+      </c>
+      <c r="B12" t="n">
+        <v>371.5206611570247</v>
+      </c>
+      <c r="C12" t="n">
+        <v>403.396694214876</v>
+      </c>
+      <c r="D12" t="n">
+        <v>426.4793388429752</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>257.2066115702479</v>
+      </c>
+      <c r="B13" t="n">
+        <v>371.5206611570247</v>
+      </c>
+      <c r="C13" t="n">
+        <v>290.1818181818181</v>
+      </c>
+      <c r="D13" t="n">
+        <v>426.4793388429752</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>294.5785123966942</v>
+      </c>
+      <c r="B14" t="n">
+        <v>535.297520661157</v>
+      </c>
+      <c r="C14" t="n">
+        <v>326.4545454545454</v>
+      </c>
+      <c r="D14" t="n">
+        <v>583.6611570247933</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>157.1818181818182</v>
+      </c>
+      <c r="B15" t="n">
+        <v>535.297520661157</v>
+      </c>
+      <c r="C15" t="n">
+        <v>189.0578512396694</v>
+      </c>
+      <c r="D15" t="n">
+        <v>583.6611570247933</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>334.1487603305785</v>
+      </c>
+      <c r="B16" t="n">
+        <v>583.6611570247933</v>
+      </c>
+      <c r="C16" t="n">
+        <v>368.2231404958677</v>
+      </c>
+      <c r="D16" t="n">
+        <v>634.2231404958677</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>173.6694214876033</v>
+      </c>
+      <c r="B17" t="n">
+        <v>583.6611570247933</v>
+      </c>
+      <c r="C17" t="n">
+        <v>207.7438016528925</v>
+      </c>
+      <c r="D17" t="n">
+        <v>634.2231404958677</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>204.4462809917355</v>
+      </c>
+      <c r="B18" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C18" t="n">
+        <v>237.4214876033058</v>
+      </c>
+      <c r="D18" t="n">
+        <v>686.9834710743801</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>52.7603305785124</v>
+      </c>
+      <c r="B19" t="n">
+        <v>634.2231404958677</v>
+      </c>
+      <c r="C19" t="n">
+        <v>86.83471074380165</v>
+      </c>
+      <c r="D19" t="n">
+        <v>686.9834710743801</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>345.1404958677685</v>
+      </c>
+      <c r="B20" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C20" t="n">
+        <v>375.9173553719008</v>
+      </c>
+      <c r="D20" t="n">
+        <v>741.9421487603305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>200.0495867768595</v>
+      </c>
+      <c r="B21" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C21" t="n">
+        <v>231.9256198347107</v>
+      </c>
+      <c r="D21" t="n">
+        <v>741.9421487603305</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>51.66115702479338</v>
+      </c>
+      <c r="B22" t="n">
+        <v>686.9834710743801</v>
+      </c>
+      <c r="C22" t="n">
+        <v>83.53719008264461</v>
+      </c>
+      <c r="D22" t="n">
+        <v>741.9421487603305</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>345.1404958677685</v>
+      </c>
+      <c r="B23" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C23" t="n">
+        <v>378.1157024793388</v>
+      </c>
+      <c r="D23" t="n">
+        <v>795.8016528925619</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>153.8842975206611</v>
+      </c>
+      <c r="B24" t="n">
+        <v>741.9421487603305</v>
+      </c>
+      <c r="C24" t="n">
+        <v>186.8595041322314</v>
+      </c>
+      <c r="D24" t="n">
+        <v>795.8016528925619</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>